--- a/assessment_forms/044_spiritual_gifts_assessment--assessment_forms.xlsx
+++ b/assessment_forms/044_spiritual_gifts_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_had_a_deep_sense_of_peace_that_i_could_not_explain.'}</t>
+          <t>i_have_had_a_deep_sense_of_peace_that_i_could_not_explain.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I have had a deep sense of peace that I could not explain.'}</t>
+          <t>I have had a deep sense of peace that I could not explain.</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_have_a_deep_sense_of_peace_that_i_could_not_explain.'}</t>
+          <t>i_do_not_have_a_deep_sense_of_peace_that_i_could_not_explain.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I do not have a deep sense of peace that I could not explain.'}</t>
+          <t>I do not have a deep sense of peace that I could not explain.</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_not_sure.'}</t>
+          <t>i_am_not_sure.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'I am not sure.'}</t>
+          <t>I am not sure.</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_"i_have_a_deep_sense_of_knowing_that_i_can't_explain."}</t>
+          <t>i_have_a_deep_sense_of_knowing_that_i_can't_explain.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': "I have a deep sense of knowing that I can't explain."}</t>
+          <t>I have a deep sense of knowing that I can't explain.</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_"i_have_been_given_specific,_unique_words_to_say_or_write_that_i_couldn't_explain."}</t>
+          <t>i_have_been_given_specific,_unique_words_to_say_or_write_that_i_couldn't_explain.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': "I have been given specific, unique words to say or write that I couldn't explain."}</t>
+          <t>I have been given specific, unique words to say or write that I couldn't explain.</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_not_sure.'}</t>
+          <t>i_am_not_sure.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I am not sure.'}</t>
+          <t>I am not sure.</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_"i_have_been_given_specific,_unique_words_to_say_or_write_that_i_couldn't_explain."}</t>
+          <t>i_have_been_given_specific,_unique_words_to_say_or_write_that_i_couldn't_explain.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': "I have been given specific, unique words to say or write that I couldn't explain."}</t>
+          <t>I have been given specific, unique words to say or write that I couldn't explain.</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_"i_have_been_given_a_deep_sense_of_knowing_that_i_couldn't_explain."}</t>
+          <t>i_have_been_given_a_deep_sense_of_knowing_that_i_couldn't_explain.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': "I have been given a deep sense of knowing that I couldn't explain."}</t>
+          <t>I have been given a deep sense of knowing that I couldn't explain.</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'i_am_not_sure.'}</t>
+          <t>i_am_not_sure.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'I am not sure.'}</t>
+          <t>I am not sure.</t>
         </is>
       </c>
     </row>
